--- a/StructureDefinition-VunsPatient.xlsx
+++ b/StructureDefinition-VunsPatient.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$94</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3561" uniqueCount="594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3523" uniqueCount="590">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T18:27:09+01:00</t>
+    <t>2026-10-15T09:50:14+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -437,7 +437,7 @@
     <t>Patient.meta.profile</t>
   </si>
   <si>
-    <t>3</t>
+    <t>2</t>
   </si>
   <si>
     <t xml:space="preserve">canonical(StructureDefinition)
@@ -473,15 +473,6 @@
   </si>
   <si>
     <t>https://www.ehealth.fgov.be/standards/fhir/core/StructureDefinition/be-patient</t>
-  </si>
-  <si>
-    <t>Patient.meta.profile:euIpsPatient</t>
-  </si>
-  <si>
-    <t>euIpsPatient</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/uv/ips/StructureDefinition/Patient-uv-ips</t>
   </si>
   <si>
     <t>Patient.meta.security</t>
@@ -1069,9 +1060,6 @@
   </si>
   <si>
     <t>Patient.telecom</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t xml:space="preserve">ContactPoint
@@ -2182,7 +2170,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO95"/>
+  <dimension ref="A1:AO94"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="43.40234375" customWidth="true" bestFit="true"/>
@@ -3640,20 +3628,18 @@
         <v>147</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="C13" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
         <v>19</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>19</v>
@@ -3665,16 +3651,16 @@
         <v>88</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3685,7 +3671,7 @@
         <v>19</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>149</v>
+        <v>19</v>
       </c>
       <c r="T13" t="s" s="2">
         <v>19</v>
@@ -3700,13 +3686,13 @@
         <v>19</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>19</v>
+        <v>152</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>19</v>
+        <v>153</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>19</v>
+        <v>154</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>19</v>
@@ -3724,7 +3710,7 @@
         <v>19</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3756,10 +3742,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3782,16 +3768,16 @@
         <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3817,13 +3803,13 @@
         <v>19</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>19</v>
@@ -3841,7 +3827,7 @@
         <v>19</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3873,10 +3859,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3887,28 +3873,28 @@
         <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3934,13 +3920,13 @@
         <v>19</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>163</v>
+        <v>19</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>164</v>
+        <v>19</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>165</v>
+        <v>19</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>19</v>
@@ -3958,13 +3944,13 @@
         <v>19</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>19</v>
@@ -3990,10 +3976,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4010,22 +3996,22 @@
         <v>19</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>129</v>
+        <v>170</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4051,13 +4037,13 @@
         <v>19</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>19</v>
+        <v>174</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>19</v>
+        <v>175</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>19</v>
+        <v>176</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>19</v>
@@ -4075,7 +4061,7 @@
         <v>19</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -4107,14 +4093,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>19</v>
+        <v>179</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4133,16 +4119,16 @@
         <v>19</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4168,13 +4154,13 @@
         <v>19</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>177</v>
+        <v>19</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>178</v>
+        <v>19</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>179</v>
+        <v>19</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>19</v>
@@ -4192,7 +4178,7 @@
         <v>19</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -4207,7 +4193,7 @@
         <v>99</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>19</v>
+        <v>185</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>19</v>
@@ -4224,21 +4210,21 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>19</v>
@@ -4250,16 +4236,16 @@
         <v>19</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4309,22 +4295,22 @@
         <v>19</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>19</v>
@@ -4341,14 +4327,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>190</v>
+        <v>19</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4367,17 +4353,15 @@
         <v>19</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>191</v>
+        <v>108</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>194</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>19</v>
@@ -4414,19 +4398,17 @@
         <v>19</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="AC19" s="2"/>
       <c r="AD19" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4438,10 +4420,10 @@
         <v>19</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>196</v>
+        <v>19</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>19</v>
@@ -4458,12 +4440,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="D20" t="s" s="2">
         <v>19</v>
       </c>
@@ -4472,7 +4456,7 @@
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>19</v>
@@ -4484,13 +4468,13 @@
         <v>19</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>108</v>
+        <v>200</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4529,17 +4513,19 @@
         <v>19</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AC20" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="AD20" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>114</v>
+        <v>19</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4571,14 +4557,12 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="C21" t="s" s="2">
-        <v>202</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
         <v>19</v>
       </c>
@@ -4599,13 +4583,13 @@
         <v>19</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>203</v>
+        <v>89</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>204</v>
+        <v>102</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>205</v>
+        <v>103</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4656,22 +4640,22 @@
         <v>19</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>19</v>
+        <v>205</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>116</v>
+        <v>19</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>19</v>
@@ -4702,7 +4686,7 @@
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>19</v>
@@ -4714,13 +4698,13 @@
         <v>19</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>102</v>
+        <v>195</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>103</v>
+        <v>196</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4759,34 +4743,34 @@
         <v>19</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>19</v>
+        <v>112</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>208</v>
+        <v>19</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>105</v>
+        <v>19</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>19</v>
@@ -4803,10 +4787,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="B23" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4814,10 +4798,10 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>19</v>
@@ -4829,22 +4813,24 @@
         <v>19</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>19</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>19</v>
+        <v>213</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>19</v>
@@ -4874,34 +4860,34 @@
         <v>19</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>112</v>
+        <v>19</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>114</v>
+        <v>19</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>115</v>
+        <v>214</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>116</v>
+        <v>19</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>19</v>
+        <v>193</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>19</v>
@@ -4918,10 +4904,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4944,24 +4930,22 @@
         <v>19</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>129</v>
+        <v>217</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>215</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>19</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>216</v>
+        <v>19</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>19</v>
@@ -5003,22 +4987,22 @@
         <v>19</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>19</v>
+        <v>221</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>19</v>
+        <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>19</v>
@@ -5035,21 +5019,23 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="C25" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="D25" t="s" s="2">
         <v>19</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>19</v>
@@ -5061,13 +5047,13 @@
         <v>19</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -5118,22 +5104,22 @@
         <v>19</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>224</v>
+        <v>19</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>196</v>
+        <v>19</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>19</v>
@@ -5150,13 +5136,13 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>19</v>
@@ -5178,13 +5164,13 @@
         <v>19</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5235,7 +5221,7 @@
         <v>19</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -5267,13 +5253,13 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>19</v>
@@ -5295,13 +5281,13 @@
         <v>19</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5352,7 +5338,7 @@
         <v>19</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -5384,16 +5370,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="C28" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5406,13 +5390,13 @@
         <v>19</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J28" t="s" s="2">
         <v>19</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>237</v>
+        <v>108</v>
       </c>
       <c r="L28" t="s" s="2">
         <v>238</v>
@@ -5420,8 +5404,12 @@
       <c r="M28" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
+      <c r="N28" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>19</v>
       </c>
@@ -5469,7 +5457,7 @@
         <v>19</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>200</v>
+        <v>241</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5484,7 +5472,7 @@
         <v>116</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>19</v>
+        <v>193</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>19</v>
@@ -5501,14 +5489,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>107</v>
+        <v>19</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5521,25 +5509,23 @@
         <v>19</v>
       </c>
       <c r="I29" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J29" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="J29" t="s" s="2">
-        <v>19</v>
-      </c>
       <c r="K29" t="s" s="2">
-        <v>108</v>
+        <v>243</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>19</v>
@@ -5588,7 +5574,7 @@
         <v>19</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5600,19 +5586,19 @@
         <v>19</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>196</v>
+        <v>247</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>19</v>
+        <v>248</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>19</v>
+        <v>249</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>19</v>
+        <v>250</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>19</v>
@@ -5620,10 +5606,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5634,34 +5620,38 @@
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J30" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>255</v>
+      </c>
       <c r="O30" t="s" s="2">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>19</v>
       </c>
-      <c r="Q30" s="2"/>
+      <c r="Q30" t="s" s="2">
+        <v>257</v>
+      </c>
       <c r="R30" t="s" s="2">
         <v>19</v>
       </c>
@@ -5705,13 +5695,13 @@
         <v>19</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>19</v>
@@ -5720,16 +5710,16 @@
         <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>251</v>
+        <v>105</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>253</v>
+        <v>19</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>19</v>
@@ -5737,10 +5727,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5748,109 +5738,107 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J31" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>19</v>
       </c>
-      <c r="Q31" t="s" s="2">
+      <c r="Q31" s="2"/>
+      <c r="R31" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S31" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T31" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF31" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="R31" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="S31" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="T31" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="U31" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="V31" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="W31" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="X31" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y31" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Z31" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AA31" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB31" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>254</v>
-      </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>99</v>
+        <v>266</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>105</v>
+        <v>268</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>262</v>
+        <v>19</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>19</v>
+        <v>269</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>19</v>
@@ -5858,10 +5846,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5869,35 +5857,31 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G32" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="G32" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H32" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>19</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>264</v>
+        <v>101</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>265</v>
+        <v>102</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>268</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>19</v>
       </c>
@@ -5945,31 +5929,31 @@
         <v>19</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>263</v>
+        <v>104</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>269</v>
+        <v>19</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>270</v>
+        <v>105</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>271</v>
+        <v>19</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>272</v>
+        <v>19</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>19</v>
@@ -5977,21 +5961,21 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>19</v>
@@ -6003,15 +5987,17 @@
         <v>19</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>19</v>
@@ -6048,31 +6034,31 @@
         <v>19</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>19</v>
+        <v>112</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>105</v>
@@ -6092,14 +6078,16 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="C34" s="2"/>
+        <v>271</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="D34" t="s" s="2">
-        <v>107</v>
+        <v>19</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6118,17 +6106,15 @@
         <v>19</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>108</v>
+        <v>274</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>109</v>
+        <v>275</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>19</v>
@@ -6165,16 +6151,16 @@
         <v>19</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>112</v>
+        <v>19</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>114</v>
+        <v>19</v>
       </c>
       <c r="AF34" t="s" s="2">
         <v>115</v>
@@ -6192,7 +6178,7 @@
         <v>116</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>105</v>
+        <v>276</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>19</v>
@@ -6209,14 +6195,12 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="C35" t="s" s="2">
-        <v>276</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
         <v>19</v>
       </c>
@@ -6225,28 +6209,32 @@
         <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>277</v>
+        <v>170</v>
       </c>
       <c r="L35" t="s" s="2">
         <v>278</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
+        <v>279</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>19</v>
       </c>
@@ -6270,13 +6258,13 @@
         <v>19</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>19</v>
+        <v>282</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>19</v>
+        <v>283</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>19</v>
+        <v>284</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>19</v>
@@ -6294,22 +6282,22 @@
         <v>19</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>115</v>
+        <v>285</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>19</v>
@@ -6318,7 +6306,7 @@
         <v>19</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>19</v>
+        <v>287</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>19</v>
@@ -6326,10 +6314,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6346,25 +6334,25 @@
         <v>19</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J36" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>173</v>
+        <v>101</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>19</v>
@@ -6389,13 +6377,13 @@
         <v>19</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>285</v>
+        <v>19</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>286</v>
+        <v>19</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>287</v>
+        <v>19</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>19</v>
@@ -6413,7 +6401,7 @@
         <v>19</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6428,7 +6416,7 @@
         <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>19</v>
@@ -6437,7 +6425,7 @@
         <v>19</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>19</v>
@@ -6445,14 +6433,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>19</v>
+        <v>297</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6474,17 +6462,15 @@
         <v>101</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>295</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>19</v>
       </c>
@@ -6496,7 +6482,7 @@
         <v>19</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>19</v>
+        <v>301</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>19</v>
@@ -6532,7 +6518,7 @@
         <v>19</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6547,7 +6533,7 @@
         <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>19</v>
@@ -6556,7 +6542,7 @@
         <v>19</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>19</v>
@@ -6564,21 +6550,21 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>19</v>
@@ -6593,13 +6579,13 @@
         <v>101</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6613,7 +6599,7 @@
         <v>19</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>304</v>
+        <v>19</v>
       </c>
       <c r="U38" t="s" s="2">
         <v>19</v>
@@ -6649,13 +6635,13 @@
         <v>19</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>19</v>
@@ -6664,7 +6650,7 @@
         <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>19</v>
@@ -6673,7 +6659,7 @@
         <v>19</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>19</v>
@@ -6681,14 +6667,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>309</v>
+        <v>19</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6710,14 +6696,12 @@
         <v>101</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>312</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>19</v>
@@ -6766,7 +6750,7 @@
         <v>19</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6781,7 +6765,7 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>19</v>
@@ -6790,7 +6774,7 @@
         <v>19</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>19</v>
@@ -6798,10 +6782,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6827,10 +6811,10 @@
         <v>101</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6881,7 +6865,7 @@
         <v>19</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6896,7 +6880,7 @@
         <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>19</v>
@@ -6905,7 +6889,7 @@
         <v>19</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>19</v>
@@ -6913,10 +6897,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6927,7 +6911,7 @@
         <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>19</v>
@@ -6939,16 +6923,18 @@
         <v>88</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>101</v>
+        <v>326</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+      <c r="O41" t="s" s="2">
+        <v>329</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>19</v>
       </c>
@@ -6996,13 +6982,13 @@
         <v>19</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>19</v>
@@ -7011,7 +6997,7 @@
         <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>19</v>
@@ -7020,7 +7006,7 @@
         <v>19</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>19</v>
@@ -7028,10 +7014,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7039,10 +7025,10 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>78</v>
+        <v>135</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>19</v>
@@ -7054,17 +7040,19 @@
         <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>336</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>337</v>
+      </c>
       <c r="O42" t="s" s="2">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>19</v>
@@ -7101,16 +7089,14 @@
         <v>19</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>339</v>
+      </c>
+      <c r="AC42" s="2"/>
       <c r="AD42" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="AF42" t="s" s="2">
         <v>333</v>
@@ -7119,7 +7105,7 @@
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>19</v>
@@ -7128,16 +7114,16 @@
         <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>19</v>
+        <v>341</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>19</v>
@@ -7145,24 +7131,26 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="C43" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="C43" t="s" s="2">
+        <v>344</v>
+      </c>
       <c r="D43" t="s" s="2">
         <v>19</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>337</v>
+        <v>87</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>19</v>
@@ -7171,19 +7159,19 @@
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="O43" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>19</v>
@@ -7220,17 +7208,19 @@
         <v>19</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="AC43" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="AD43" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>114</v>
+        <v>19</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7245,16 +7235,16 @@
         <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>19</v>
@@ -7262,48 +7252,42 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="C44" t="s" s="2">
-        <v>348</v>
-      </c>
+        <v>346</v>
+      </c>
+      <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>19</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G44" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="G44" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H44" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>19</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>338</v>
+        <v>101</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>339</v>
+        <v>102</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>342</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>19</v>
       </c>
@@ -7351,31 +7335,31 @@
         <v>19</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>336</v>
+        <v>104</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>344</v>
+        <v>105</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>345</v>
+        <v>19</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>346</v>
+        <v>19</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>19</v>
@@ -7383,21 +7367,21 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>19</v>
@@ -7409,15 +7393,17 @@
         <v>19</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>19</v>
@@ -7454,31 +7440,31 @@
         <v>19</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>19</v>
+        <v>112</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>105</v>
@@ -7498,21 +7484,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>107</v>
+        <v>19</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>19</v>
@@ -7521,20 +7507,18 @@
         <v>19</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>108</v>
+        <v>170</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>109</v>
+        <v>351</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>19</v>
@@ -7544,7 +7528,7 @@
         <v>19</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>19</v>
+        <v>344</v>
       </c>
       <c r="T46" t="s" s="2">
         <v>19</v>
@@ -7559,46 +7543,46 @@
         <v>19</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>19</v>
+        <v>282</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>19</v>
+        <v>353</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>19</v>
+        <v>354</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>112</v>
+        <v>19</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>114</v>
+        <v>19</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>115</v>
+        <v>355</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>19</v>
+        <v>356</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>105</v>
+        <v>357</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>19</v>
@@ -7607,7 +7591,7 @@
         <v>19</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>19</v>
+        <v>358</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>19</v>
@@ -7615,10 +7599,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7626,7 +7610,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>87</v>
@@ -7641,16 +7625,20 @@
         <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>173</v>
+        <v>101</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+        <v>362</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>364</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>19</v>
       </c>
@@ -7659,7 +7647,7 @@
         <v>19</v>
       </c>
       <c r="S47" t="s" s="2">
-        <v>348</v>
+        <v>19</v>
       </c>
       <c r="T47" t="s" s="2">
         <v>19</v>
@@ -7674,13 +7662,13 @@
         <v>19</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>285</v>
+        <v>19</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>357</v>
+        <v>19</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>358</v>
+        <v>19</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>19</v>
@@ -7698,7 +7686,7 @@
         <v>19</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7707,13 +7695,13 @@
         <v>87</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>360</v>
+        <v>19</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>99</v>
+        <v>366</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>19</v>
@@ -7722,7 +7710,7 @@
         <v>19</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>19</v>
@@ -7730,10 +7718,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7750,25 +7738,25 @@
         <v>19</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J48" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>101</v>
+        <v>170</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>19</v>
@@ -7793,13 +7781,13 @@
         <v>19</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>19</v>
+        <v>282</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>19</v>
+        <v>375</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>19</v>
+        <v>376</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>19</v>
@@ -7817,7 +7805,7 @@
         <v>19</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7829,10 +7817,10 @@
         <v>19</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>370</v>
+        <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>371</v>
+        <v>286</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>19</v>
@@ -7841,7 +7829,7 @@
         <v>19</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>19</v>
@@ -7849,10 +7837,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7869,26 +7857,24 @@
         <v>19</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J49" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>173</v>
+        <v>381</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>378</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>19</v>
       </c>
@@ -7912,13 +7898,13 @@
         <v>19</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>285</v>
+        <v>19</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>379</v>
+        <v>19</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>380</v>
+        <v>19</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>19</v>
@@ -7936,7 +7922,7 @@
         <v>19</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7951,7 +7937,7 @@
         <v>99</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>289</v>
+        <v>105</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>19</v>
@@ -7960,7 +7946,7 @@
         <v>19</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>382</v>
+        <v>105</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>19</v>
@@ -7968,10 +7954,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7994,17 +7980,15 @@
         <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>385</v>
+        <v>326</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>388</v>
-      </c>
+        <v>389</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>19</v>
@@ -8053,7 +8037,7 @@
         <v>19</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -8068,7 +8052,7 @@
         <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>105</v>
+        <v>331</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>19</v>
@@ -8077,7 +8061,7 @@
         <v>19</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>105</v>
+        <v>193</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>19</v>
@@ -8085,24 +8069,26 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="C51" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="C51" t="s" s="2">
+        <v>392</v>
+      </c>
       <c r="D51" t="s" s="2">
         <v>19</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>19</v>
@@ -8111,16 +8097,20 @@
         <v>88</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>392</v>
+        <v>335</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+        <v>336</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>19</v>
       </c>
@@ -8168,13 +8158,13 @@
         <v>19</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>394</v>
+        <v>333</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>19</v>
@@ -8183,16 +8173,16 @@
         <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>19</v>
+        <v>341</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>196</v>
+        <v>342</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>19</v>
@@ -8200,48 +8190,42 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="C52" t="s" s="2">
-        <v>396</v>
-      </c>
+        <v>346</v>
+      </c>
+      <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>19</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>19</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>338</v>
+        <v>101</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>339</v>
+        <v>102</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>342</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>19</v>
       </c>
@@ -8289,31 +8273,31 @@
         <v>19</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>336</v>
+        <v>104</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>344</v>
+        <v>105</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>345</v>
+        <v>19</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>346</v>
+        <v>19</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>19</v>
@@ -8321,21 +8305,21 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>19</v>
@@ -8347,15 +8331,17 @@
         <v>19</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>19</v>
@@ -8392,31 +8378,31 @@
         <v>19</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>19</v>
+        <v>112</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>105</v>
@@ -8436,21 +8422,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>107</v>
+        <v>19</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>19</v>
@@ -8459,20 +8445,18 @@
         <v>19</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>108</v>
+        <v>170</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>109</v>
+        <v>351</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>19</v>
@@ -8482,7 +8466,7 @@
         <v>19</v>
       </c>
       <c r="S54" t="s" s="2">
-        <v>19</v>
+        <v>392</v>
       </c>
       <c r="T54" t="s" s="2">
         <v>19</v>
@@ -8497,46 +8481,46 @@
         <v>19</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>19</v>
+        <v>282</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>19</v>
+        <v>353</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>19</v>
+        <v>354</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>112</v>
+        <v>19</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>114</v>
+        <v>19</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>115</v>
+        <v>355</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>19</v>
+        <v>356</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>105</v>
+        <v>357</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>19</v>
@@ -8545,7 +8529,7 @@
         <v>19</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>19</v>
+        <v>358</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>19</v>
@@ -8553,10 +8537,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8564,7 +8548,7 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>87</v>
@@ -8579,16 +8563,20 @@
         <v>88</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>173</v>
+        <v>101</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
+        <v>362</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>364</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>19</v>
       </c>
@@ -8597,7 +8585,7 @@
         <v>19</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>396</v>
+        <v>19</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>19</v>
@@ -8612,13 +8600,13 @@
         <v>19</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>285</v>
+        <v>19</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>357</v>
+        <v>19</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>358</v>
+        <v>19</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>19</v>
@@ -8636,7 +8624,7 @@
         <v>19</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8645,13 +8633,13 @@
         <v>87</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>360</v>
+        <v>19</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>99</v>
+        <v>397</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>19</v>
@@ -8660,7 +8648,7 @@
         <v>19</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>19</v>
@@ -8668,10 +8656,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8688,25 +8676,25 @@
         <v>19</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J56" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>101</v>
+        <v>170</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>19</v>
@@ -8731,13 +8719,13 @@
         <v>19</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>19</v>
+        <v>282</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>19</v>
+        <v>375</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>19</v>
+        <v>376</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>19</v>
@@ -8755,7 +8743,7 @@
         <v>19</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8767,10 +8755,10 @@
         <v>19</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>401</v>
+        <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>371</v>
+        <v>286</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>19</v>
@@ -8779,7 +8767,7 @@
         <v>19</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>19</v>
@@ -8787,10 +8775,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8807,26 +8795,24 @@
         <v>19</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J57" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>173</v>
+        <v>381</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>378</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>19</v>
       </c>
@@ -8850,13 +8836,13 @@
         <v>19</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>285</v>
+        <v>19</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>379</v>
+        <v>19</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>380</v>
+        <v>19</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>19</v>
@@ -8874,7 +8860,7 @@
         <v>19</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8889,7 +8875,7 @@
         <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>289</v>
+        <v>105</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>19</v>
@@ -8898,7 +8884,7 @@
         <v>19</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>382</v>
+        <v>105</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>19</v>
@@ -8906,10 +8892,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8932,17 +8918,15 @@
         <v>88</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>385</v>
+        <v>326</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>388</v>
-      </c>
+        <v>389</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>19</v>
@@ -8991,7 +8975,7 @@
         <v>19</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -9006,7 +8990,7 @@
         <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>105</v>
+        <v>331</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>19</v>
@@ -9015,7 +8999,7 @@
         <v>19</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>105</v>
+        <v>193</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>19</v>
@@ -9023,10 +9007,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9034,13 +9018,13 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>19</v>
@@ -9049,16 +9033,20 @@
         <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>329</v>
+        <v>170</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+        <v>403</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>405</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>19</v>
       </c>
@@ -9082,13 +9070,13 @@
         <v>19</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>19</v>
+        <v>282</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>19</v>
+        <v>406</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>19</v>
+        <v>407</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>19</v>
@@ -9106,7 +9094,7 @@
         <v>19</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9121,16 +9109,16 @@
         <v>99</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>334</v>
+        <v>408</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>19</v>
+        <v>409</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>196</v>
+        <v>410</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>19</v>
@@ -9138,10 +9126,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9155,7 +9143,7 @@
         <v>87</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>19</v>
@@ -9164,19 +9152,19 @@
         <v>88</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>173</v>
+        <v>412</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>19</v>
@@ -9201,31 +9189,31 @@
         <v>19</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>285</v>
+        <v>19</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>410</v>
+        <v>19</v>
       </c>
       <c r="Z60" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF60" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9240,27 +9228,27 @@
         <v>99</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>19</v>
+        <v>420</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9268,7 +9256,7 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>87</v>
@@ -9280,23 +9268,19 @@
         <v>19</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>416</v>
+        <v>101</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>420</v>
-      </c>
+        <v>423</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>19</v>
       </c>
@@ -9344,7 +9328,7 @@
         <v>19</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>415</v>
+        <v>104</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9356,30 +9340,30 @@
         <v>19</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>421</v>
+        <v>19</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>422</v>
+        <v>19</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>423</v>
+        <v>19</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>424</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9390,7 +9374,7 @@
         <v>78</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>19</v>
@@ -9402,13 +9386,13 @@
         <v>19</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>426</v>
+        <v>195</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>427</v>
+        <v>196</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9447,31 +9431,29 @@
         <v>19</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="AC62" s="2"/>
       <c r="AD62" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>19</v>
@@ -9491,12 +9473,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="C63" s="2"/>
+        <v>424</v>
+      </c>
+      <c r="C63" t="s" s="2">
+        <v>426</v>
+      </c>
       <c r="D63" t="s" s="2">
         <v>19</v>
       </c>
@@ -9505,7 +9489,7 @@
         <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>19</v>
@@ -9517,13 +9501,13 @@
         <v>19</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>108</v>
+        <v>274</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>198</v>
+        <v>427</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>199</v>
+        <v>427</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9562,14 +9546,16 @@
         <v>19</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AC63" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="AD63" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>114</v>
+        <v>19</v>
       </c>
       <c r="AF63" t="s" s="2">
         <v>115</v>
@@ -9587,7 +9573,7 @@
         <v>116</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>19</v>
+        <v>276</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>19</v>
@@ -9604,14 +9590,12 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="C64" t="s" s="2">
-        <v>430</v>
-      </c>
+      <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
         <v>19</v>
       </c>
@@ -9632,13 +9616,13 @@
         <v>19</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>277</v>
+        <v>412</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9689,22 +9673,22 @@
         <v>19</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>115</v>
+        <v>431</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>116</v>
+        <v>19</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>279</v>
+        <v>19</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>19</v>
@@ -9741,22 +9725,26 @@
         <v>19</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>416</v>
+        <v>433</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
+        <v>435</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>437</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>19</v>
       </c>
@@ -9804,7 +9792,7 @@
         <v>19</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9816,19 +9804,19 @@
         <v>19</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>19</v>
+        <v>99</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>19</v>
+        <v>438</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>19</v>
+        <v>439</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>19</v>
@@ -9836,10 +9824,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9850,31 +9838,31 @@
         <v>78</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J66" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>437</v>
+        <v>217</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>19</v>
@@ -9923,13 +9911,13 @@
         <v>19</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>19</v>
@@ -9938,16 +9926,16 @@
         <v>99</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>105</v>
+        <v>446</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>19</v>
@@ -9955,10 +9943,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9969,7 +9957,7 @@
         <v>78</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>19</v>
@@ -9978,22 +9966,20 @@
         <v>19</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>220</v>
+        <v>449</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>447</v>
-      </c>
+        <v>451</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>19</v>
@@ -10018,13 +10004,13 @@
         <v>19</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>19</v>
+        <v>152</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>19</v>
+        <v>453</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>19</v>
+        <v>454</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>19</v>
@@ -10042,13 +10028,13 @@
         <v>19</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>19</v>
@@ -10057,16 +10043,16 @@
         <v>99</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>19</v>
@@ -10074,10 +10060,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10100,17 +10086,19 @@
         <v>19</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>461</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>462</v>
+      </c>
       <c r="O68" t="s" s="2">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>19</v>
@@ -10135,31 +10123,31 @@
         <v>19</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>155</v>
+        <v>19</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>457</v>
+        <v>19</v>
       </c>
       <c r="Z68" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF68" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10174,16 +10162,16 @@
         <v>99</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>460</v>
+        <v>105</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>19</v>
@@ -10191,10 +10179,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10205,7 +10193,7 @@
         <v>78</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>19</v>
@@ -10217,19 +10205,19 @@
         <v>19</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>19</v>
@@ -10278,13 +10266,13 @@
         <v>19</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>19</v>
@@ -10293,7 +10281,7 @@
         <v>99</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>105</v>
@@ -10302,7 +10290,7 @@
         <v>19</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>19</v>
@@ -10310,10 +10298,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10336,19 +10324,19 @@
         <v>19</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>19</v>
@@ -10397,7 +10385,7 @@
         <v>19</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10409,10 +10397,10 @@
         <v>19</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>99</v>
+        <v>480</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>105</v>
@@ -10421,7 +10409,7 @@
         <v>19</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>477</v>
+        <v>19</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>19</v>
@@ -10429,10 +10417,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10443,7 +10431,7 @@
         <v>78</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>19</v>
@@ -10455,20 +10443,16 @@
         <v>19</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>479</v>
+        <v>101</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>480</v>
+        <v>102</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>483</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>19</v>
       </c>
@@ -10516,25 +10500,25 @@
         <v>19</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>478</v>
+        <v>104</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>484</v>
+        <v>19</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>485</v>
+        <v>105</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>105</v>
+        <v>19</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>19</v>
@@ -10548,21 +10532,21 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>19</v>
@@ -10574,15 +10558,17 @@
         <v>19</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>19</v>
@@ -10631,19 +10617,19 @@
         <v>19</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>105</v>
@@ -10663,14 +10649,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>107</v>
+        <v>485</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10683,24 +10669,26 @@
         <v>19</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K73" t="s" s="2">
         <v>108</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>109</v>
+        <v>486</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>110</v>
+        <v>487</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="O73" s="2"/>
+      <c r="O73" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>19</v>
       </c>
@@ -10748,7 +10736,7 @@
         <v>19</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>115</v>
+        <v>488</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10763,7 +10751,7 @@
         <v>116</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>105</v>
+        <v>193</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>19</v>
@@ -10780,14 +10768,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>489</v>
+        <v>19</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10800,25 +10788,23 @@
         <v>19</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>108</v>
+        <v>490</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>492</v>
+      </c>
+      <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>243</v>
+        <v>493</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>19</v>
@@ -10843,13 +10829,13 @@
         <v>19</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>19</v>
+        <v>152</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>19</v>
+        <v>494</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>19</v>
+        <v>495</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>19</v>
@@ -10867,7 +10853,7 @@
         <v>19</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10879,19 +10865,19 @@
         <v>19</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>196</v>
+        <v>496</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>19</v>
+        <v>497</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>19</v>
@@ -10899,10 +10885,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10913,7 +10899,7 @@
         <v>78</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>19</v>
@@ -10925,17 +10911,17 @@
         <v>19</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>494</v>
+        <v>261</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>19</v>
@@ -10960,37 +10946,37 @@
         <v>19</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>155</v>
+        <v>19</v>
       </c>
       <c r="Y75" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF75" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="Z75" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>493</v>
-      </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>19</v>
@@ -10999,7 +10985,7 @@
         <v>99</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>500</v>
+        <v>267</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>105</v>
@@ -11008,7 +10994,7 @@
         <v>19</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>19</v>
@@ -11016,10 +11002,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11030,7 +11016,7 @@
         <v>78</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>19</v>
@@ -11042,17 +11028,19 @@
         <v>19</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>264</v>
+        <v>334</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="N76" s="2"/>
+        <v>505</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>506</v>
+      </c>
       <c r="O76" t="s" s="2">
-        <v>505</v>
+        <v>338</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>19</v>
@@ -11101,13 +11089,13 @@
         <v>19</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>19</v>
@@ -11116,7 +11104,7 @@
         <v>99</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>270</v>
+        <v>340</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>105</v>
@@ -11125,7 +11113,7 @@
         <v>19</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>19</v>
@@ -11133,10 +11121,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11147,7 +11135,7 @@
         <v>78</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>19</v>
@@ -11159,19 +11147,17 @@
         <v>19</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>338</v>
+        <v>217</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="N77" t="s" s="2">
         <v>510</v>
       </c>
+      <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>342</v>
+        <v>511</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>19</v>
@@ -11220,13 +11206,13 @@
         <v>19</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>19</v>
@@ -11235,7 +11221,7 @@
         <v>99</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>344</v>
+        <v>445</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>105</v>
@@ -11244,7 +11230,7 @@
         <v>19</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>19</v>
@@ -11252,10 +11238,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11278,17 +11264,17 @@
         <v>19</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>220</v>
+        <v>170</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>19</v>
@@ -11313,13 +11299,13 @@
         <v>19</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>19</v>
+        <v>282</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>19</v>
+        <v>406</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>19</v>
+        <v>407</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>19</v>
@@ -11337,7 +11323,7 @@
         <v>19</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11352,7 +11338,7 @@
         <v>99</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>449</v>
+        <v>408</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>105</v>
@@ -11361,7 +11347,7 @@
         <v>19</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>19</v>
@@ -11369,10 +11355,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11395,17 +11381,17 @@
         <v>19</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>173</v>
+        <v>519</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>19</v>
@@ -11430,13 +11416,13 @@
         <v>19</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>285</v>
+        <v>19</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>410</v>
+        <v>19</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>411</v>
+        <v>19</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>19</v>
@@ -11454,7 +11440,7 @@
         <v>19</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11463,13 +11449,13 @@
         <v>87</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>19</v>
+        <v>523</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>412</v>
+        <v>524</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>105</v>
@@ -11478,7 +11464,7 @@
         <v>19</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>19</v>
@@ -11486,10 +11472,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11512,18 +11498,16 @@
         <v>19</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>523</v>
+        <v>326</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="N80" s="2"/>
-      <c r="O80" t="s" s="2">
-        <v>526</v>
-      </c>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>19</v>
       </c>
@@ -11571,7 +11555,7 @@
         <v>19</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11580,13 +11564,13 @@
         <v>87</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>527</v>
+        <v>19</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>105</v>
@@ -11595,7 +11579,7 @@
         <v>19</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>529</v>
+        <v>19</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>19</v>
@@ -11617,7 +11601,7 @@
         <v>78</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>19</v>
@@ -11629,7 +11613,7 @@
         <v>19</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>329</v>
+        <v>475</v>
       </c>
       <c r="L81" t="s" s="2">
         <v>531</v>
@@ -11637,8 +11621,12 @@
       <c r="M81" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
+      <c r="N81" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>534</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>19</v>
       </c>
@@ -11692,7 +11680,7 @@
         <v>78</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>19</v>
@@ -11701,10 +11689,10 @@
         <v>99</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>105</v>
+        <v>536</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>19</v>
@@ -11718,10 +11706,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11732,7 +11720,7 @@
         <v>78</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>19</v>
@@ -11744,20 +11732,16 @@
         <v>19</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>479</v>
+        <v>101</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>535</v>
+        <v>102</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>538</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N82" s="2"/>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>19</v>
       </c>
@@ -11805,25 +11789,25 @@
         <v>19</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>534</v>
+        <v>104</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>539</v>
+        <v>105</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>540</v>
+        <v>19</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>19</v>
@@ -11837,21 +11821,21 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>19</v>
@@ -11863,15 +11847,17 @@
         <v>19</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N83" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>19</v>
@@ -11920,19 +11906,19 @@
         <v>19</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>105</v>
@@ -11952,14 +11938,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>107</v>
+        <v>485</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -11972,24 +11958,26 @@
         <v>19</v>
       </c>
       <c r="I84" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K84" t="s" s="2">
         <v>108</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>109</v>
+        <v>486</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>110</v>
+        <v>487</v>
       </c>
       <c r="N84" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="O84" s="2"/>
+      <c r="O84" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>19</v>
       </c>
@@ -12037,7 +12025,7 @@
         <v>19</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>115</v>
+        <v>488</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12052,7 +12040,7 @@
         <v>116</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>105</v>
+        <v>193</v>
       </c>
       <c r="AL84" t="s" s="2">
         <v>19</v>
@@ -12069,45 +12057,45 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>489</v>
+        <v>19</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I85" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>108</v>
+        <v>449</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>490</v>
+        <v>541</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>491</v>
+        <v>542</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>111</v>
+        <v>543</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>243</v>
+        <v>544</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>19</v>
@@ -12132,13 +12120,13 @@
         <v>19</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>19</v>
+        <v>174</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>19</v>
+        <v>175</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>19</v>
+        <v>176</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>19</v>
@@ -12156,31 +12144,31 @@
         <v>19</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>492</v>
+        <v>540</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>196</v>
+        <v>545</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>19</v>
+        <v>546</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>19</v>
+        <v>547</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>19</v>
@@ -12188,10 +12176,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12199,7 +12187,7 @@
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G86" t="s" s="2">
         <v>87</v>
@@ -12214,19 +12202,19 @@
         <v>19</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>453</v>
+        <v>252</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>19</v>
@@ -12251,13 +12239,13 @@
         <v>19</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>177</v>
+        <v>19</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>178</v>
+        <v>19</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>179</v>
+        <v>19</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>19</v>
@@ -12275,10 +12263,10 @@
         <v>19</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH86" t="s" s="2">
         <v>87</v>
@@ -12290,16 +12278,16 @@
         <v>99</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>19</v>
@@ -12307,21 +12295,21 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>19</v>
+        <v>557</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>19</v>
@@ -12333,20 +12321,18 @@
         <v>19</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>255</v>
+        <v>558</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>556</v>
-      </c>
+        <v>561</v>
+      </c>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>19</v>
       </c>
@@ -12394,13 +12380,13 @@
         <v>19</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>19</v>
@@ -12409,16 +12395,16 @@
         <v>99</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>558</v>
+        <v>105</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>19</v>
@@ -12426,21 +12412,21 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>561</v>
+        <v>19</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>19</v>
@@ -12449,21 +12435,23 @@
         <v>19</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>562</v>
+        <v>519</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="O88" s="2"/>
+        <v>567</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>568</v>
+      </c>
       <c r="P88" t="s" s="2">
         <v>19</v>
       </c>
@@ -12511,13 +12499,13 @@
         <v>19</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>19</v>
@@ -12526,16 +12514,16 @@
         <v>99</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>566</v>
+        <v>524</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>105</v>
+        <v>569</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>567</v>
+        <v>19</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>19</v>
@@ -12543,10 +12531,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12557,31 +12545,31 @@
         <v>78</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I89" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J89" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>523</v>
+        <v>475</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>19</v>
@@ -12630,13 +12618,13 @@
         <v>19</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>19</v>
@@ -12645,10 +12633,10 @@
         <v>99</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>528</v>
+        <v>575</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>573</v>
+        <v>105</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>19</v>
@@ -12662,10 +12650,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12676,32 +12664,28 @@
         <v>78</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>479</v>
+        <v>101</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>575</v>
+        <v>102</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>578</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N90" s="2"/>
+      <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>19</v>
       </c>
@@ -12749,25 +12733,25 @@
         <v>19</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>574</v>
+        <v>104</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>579</v>
+        <v>105</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>105</v>
+        <v>19</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>19</v>
@@ -12781,21 +12765,21 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>19</v>
@@ -12807,15 +12791,17 @@
         <v>19</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N91" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>19</v>
@@ -12864,19 +12850,19 @@
         <v>19</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>105</v>
@@ -12896,14 +12882,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>107</v>
+        <v>485</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -12916,24 +12902,26 @@
         <v>19</v>
       </c>
       <c r="I92" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K92" t="s" s="2">
         <v>108</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>109</v>
+        <v>486</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>110</v>
+        <v>487</v>
       </c>
       <c r="N92" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="O92" s="2"/>
+      <c r="O92" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="P92" t="s" s="2">
         <v>19</v>
       </c>
@@ -12981,7 +12969,7 @@
         <v>19</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>115</v>
+        <v>488</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -12996,7 +12984,7 @@
         <v>116</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>105</v>
+        <v>193</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>19</v>
@@ -13013,46 +13001,44 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>489</v>
+        <v>19</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I93" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J93" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>108</v>
+        <v>580</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>490</v>
+        <v>581</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>491</v>
+        <v>582</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>243</v>
-      </c>
+        <v>583</v>
+      </c>
+      <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>19</v>
       </c>
@@ -13100,31 +13086,31 @@
         <v>19</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>492</v>
+        <v>579</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>196</v>
+        <v>247</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>19</v>
+        <v>584</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>19</v>
@@ -13132,10 +13118,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13158,17 +13144,15 @@
         <v>88</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>584</v>
+        <v>170</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="N94" t="s" s="2">
         <v>587</v>
       </c>
+      <c r="N94" s="2"/>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>19</v>
@@ -13193,13 +13177,13 @@
         <v>19</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>19</v>
+        <v>282</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>19</v>
+        <v>587</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>19</v>
+        <v>588</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>19</v>
@@ -13217,7 +13201,7 @@
         <v>19</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>87</v>
@@ -13232,7 +13216,7 @@
         <v>99</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>250</v>
+        <v>589</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>105</v>
@@ -13241,129 +13225,14 @@
         <v>19</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>588</v>
+        <v>19</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="95" hidden="true">
-      <c r="A95" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="B95" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="C95" s="2"/>
-      <c r="D95" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="E95" s="2"/>
-      <c r="F95" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="G95" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H95" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="I95" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J95" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K95" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="L95" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="N95" s="2"/>
-      <c r="O95" s="2"/>
-      <c r="P95" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Q95" s="2"/>
-      <c r="R95" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="S95" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="T95" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="U95" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="V95" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="W95" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="X95" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="Y95" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="Z95" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="AA95" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB95" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC95" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD95" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE95" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF95" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="AG95" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH95" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI95" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AJ95" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK95" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="AL95" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AM95" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AO95" t="s" s="2">
         <v>19</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO95">
+  <autoFilter ref="A1:AO94">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -13373,7 +13242,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI94">
+  <conditionalFormatting sqref="A2:AI93">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
